--- a/_Studying(5th_sem)/ElectricalAndSchemotechnicalEngineering/лаб4/лаб4.xlsx
+++ b/_Studying(5th_sem)/ElectricalAndSchemotechnicalEngineering/лаб4/лаб4.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\itmo\_Studying(5th_sem)\ElectricalAndSchemotechnicalEngineering\лаб4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54B502E9-4602-492F-A3D6-6FF825A7DA14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DC2508B-09FF-4FFD-BCDF-B93C6B5D2D4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="24892" windowHeight="14914" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="21840" yWindow="-1594" windowWidth="24891" windowHeight="14914" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
   <si>
     <t>Ампл. Вх, В</t>
   </si>
@@ -96,6 +96,9 @@
   </si>
   <si>
     <t>если инвертировать 1 на входе - какой на выходе инвертируется</t>
+  </si>
+  <si>
+    <t>k_occ</t>
   </si>
 </sst>
 </file>
@@ -119,7 +122,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -142,13 +145,25 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -430,12 +445,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:M22"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="21.15234375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="21.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>18</v>
       </c>
@@ -457,8 +474,11 @@
       <c r="G1" s="1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="H1" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>0.48</v>
       </c>
@@ -478,10 +498,20 @@
         <f>(0.28-0.04)/2</f>
         <v>0.12000000000000001</v>
       </c>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="F2" s="1">
+        <f>C2/B2</f>
+        <v>9.9230769230769234</v>
+      </c>
+      <c r="G2" s="1">
+        <f>E2/D2</f>
+        <v>1.2</v>
+      </c>
+      <c r="H2">
+        <f>F2/G2</f>
+        <v>8.2692307692307701</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>0.6</v>
       </c>
@@ -498,10 +528,20 @@
         <f>0.352/2</f>
         <v>0.17599999999999999</v>
       </c>
-      <c r="F3" s="1"/>
-      <c r="G3" s="1"/>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="F3" s="1">
+        <f>C3/B3</f>
+        <v>10.833333333333334</v>
+      </c>
+      <c r="G3" s="1">
+        <f>E3/D3</f>
+        <v>0.87999999999999989</v>
+      </c>
+      <c r="H3">
+        <f>F3/G3</f>
+        <v>12.310606060606062</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>0</v>
       </c>
@@ -521,7 +561,7 @@
         <v>1.59</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>1</v>
       </c>
@@ -541,27 +581,49 @@
         <v>15.3</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="B10">
+        <f>B9/B8</f>
+        <v>10.737704918032788</v>
+      </c>
+      <c r="C10">
+        <f t="shared" ref="C10:F10" si="0">C9/C8</f>
+        <v>9.9096385542168672</v>
+      </c>
+      <c r="D10">
+        <f t="shared" si="0"/>
+        <v>10.578512396694215</v>
+      </c>
+      <c r="E10">
+        <f t="shared" si="0"/>
+        <v>9.8540145985401448</v>
+      </c>
+      <c r="F10">
+        <f t="shared" si="0"/>
+        <v>9.6226415094339615</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>17</v>
       </c>
@@ -569,27 +631,27 @@
         <v>19</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>8</v>
       </c>
